--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBondFirstLBiddingDto.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBondFirstLBiddingDto.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13590" windowHeight="5985"/>
   </bookViews>
@@ -45,21 +50,12 @@
     <t>币种</t>
   </si>
   <si>
-    <t>委托开始日</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
     <t>中标状态</t>
   </si>
   <si>
-    <t>投标券面总额</t>
-  </si>
-  <si>
-    <t>中标券面总额</t>
-  </si>
-  <si>
     <t>投标标位%</t>
   </si>
   <si>
@@ -69,7 +65,19 @@
     <t>投标日</t>
   </si>
   <si>
-    <t>委托终止日</t>
+    <t>投标券面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中标券面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令开始日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令终止日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -144,74 +152,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -228,7 +168,7 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="373737"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
         <a:sysClr val="window" lastClr="FFFFFF"/>
@@ -478,7 +418,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -496,8 +436,8 @@
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="10.75" customWidth="1"/>
     <col min="8" max="8" width="13.125" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="12.5" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="17.625" customWidth="1"/>
     <col min="11" max="12" width="12.5" style="3" customWidth="1"/>
     <col min="13" max="13" width="13.5" customWidth="1"/>
     <col min="14" max="14" width="14.25" customWidth="1"/>
@@ -511,7 +451,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -532,31 +472,31 @@
         <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBondFirstLBiddingDto.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBondFirstLBiddingDto.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\GUANGZHOU\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>有效状态</t>
   </si>
@@ -78,6 +78,10 @@
   </si>
   <si>
     <t>指令终止日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前处理人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -426,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" customWidth="1"/>
@@ -444,9 +448,10 @@
     <col min="15" max="15" width="12.875" customWidth="1"/>
     <col min="16" max="16" width="12.875" style="3" customWidth="1"/>
     <col min="17" max="17" width="23.75" customWidth="1"/>
+    <col min="18" max="18" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -497,6 +502,9 @@
       </c>
       <c r="Q1" s="4" t="s">
         <v>8</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
